--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCB.xlsx
@@ -422,23 +422,446 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27.7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCB_M._CORREIA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M. Correia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCB_V._PANOV</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -484,11 +907,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,34 +969,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
         </is>
       </c>
     </row>
@@ -632,16 +1089,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1108,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112.2</v>
+        <v>119.8</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1127,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>125.9</v>
+        <v>105.7</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>15.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1146,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-13.7</v>
+        <v>14.1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>-13.7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1165,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>22.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="7">
@@ -733,10 +1190,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -749,13 +1206,13 @@
         <v>0.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -765,16 +1222,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -784,7 +1241,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
@@ -793,7 +1250,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -803,7 +1260,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C11" t="n">
         <v>0.4</v>
@@ -812,7 +1269,7 @@
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -853,7 +1310,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Below-average pace; they are more comfortable when the game stays organized in the half court.</t>
+          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
         </is>
       </c>
     </row>
@@ -865,7 +1322,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Below-average assist profile; more possessions end through direct creation than collective flow.</t>
+          <t>Above-average assist profile; expect cleaner passing sequences and more extra-pass possessions.</t>
         </is>
       </c>
     </row>
@@ -889,7 +1346,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -955,7 +1412,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control the rhythm: they are more comfortable in a controlled half-court game, so do not let them play cleanly into structure.</t>
+          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
         </is>
       </c>
     </row>
@@ -980,6 +1437,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Stay connected to spacing: their perimeter volume can bend the floor if your help and recovery are sloppy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Know the first reference: A. Gakou is a primary scorer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -994,7 +1463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1016,48 +1485,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from C. Cardoso and R. Monteiro; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are R. Monteiro and J. Sibert; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+          <t>Priority closeouts start with A. Gakou and J. Sibert; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially J. Sibert and C. Cardoso; force them away from preferred areas.</t>
+          <t>Some perimeter volume comes from R. Monteiro and M. Kegler; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially J. Sibert, A. Gakou, and R. Monteiro; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Do not lose A. Gakou and J. Sibert in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1577,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SCB_J._SIBERT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bench spacer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SCB_M._CORREIA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M. Correia</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SCB_V._PANOV</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>primary handler</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1114,7 +1870,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -1197,41 +1953,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -1243,41 +1999,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1294,36 +2050,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
         <v>1.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1335,38 +2091,48 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>31.8%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SCB_M._KEGLER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M. Kegler</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1388,11 +2154,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -1400,7 +2166,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>32.8%</t>
         </is>
       </c>
     </row>
@@ -1420,23 +2186,23 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -1456,23 +2222,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -1496,38 +2262,30 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SCB_J._SIBERT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>J. Sibert</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1536,23 +2294,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -1564,12 +2322,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1580,23 +2338,287 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SCB_A._GAKOU</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SCB_A._MOREIRA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>6</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SCB_V._PANOV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="M16" t="n">
         <v>0.7</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>54.5%</t>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCB.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,88 +515,88 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -608,47 +608,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -671,16 +671,16 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -690,17 +690,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -712,37 +712,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -764,47 +764,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -816,18 +816,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -836,32 +836,84 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SCB_A._MOREIRA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -876,24 +928,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A. Gakou | J. Sibert</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A. Gakou | R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A. Gakou | R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30.3</v>
       </c>
     </row>
   </sheetData>
@@ -907,12 +1075,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1003,34 +1171,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>lineups</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (14.6 min)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (8.2 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
         </is>
       </c>
     </row>
@@ -1089,16 +1291,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78.7</v>
+        <v>79.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -1108,16 +1310,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119.8</v>
+        <v>117.1</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>13.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -1127,16 +1329,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105.7</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="5">
@@ -1146,16 +1348,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.1</v>
+        <v>17.1</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>14.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="6">
@@ -1165,16 +1367,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7">
@@ -1190,10 +1392,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1209,7 +1411,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
@@ -1222,16 +1424,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.5</v>
+        <v>22.3</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">
@@ -1247,10 +1449,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1346,7 +1548,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1572,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Above-average three-point volume; spacing discipline and clean closeouts matter.</t>
+          <t>Perimeter volume is close to league average; shot mix alone does not define them.</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1638,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stay connected to spacing: their perimeter volume can bend the floor if your help and recovery are sloppy.</t>
+          <t>Know the first reference: A. Gakou is a spot-up shooter, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Know the first reference: A. Gakou is a primary scorer, and the plan should start with taking away his comfort.</t>
+          <t>Closeout discipline matters: A. Gakou, J. Sibert are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1490,7 +1692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The main offensive references are R. Monteiro and J. Sibert; load the scouting plan into those names first.</t>
+          <t>The main offensive references are R. Monteiro and A. Gakou; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1716,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from R. Monteiro and M. Kegler; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from J. Sibert and M. Kegler; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1538,19 +1740,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially J. Sibert, A. Gakou, and R. Monteiro; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially A. Gakou, R. Monteiro, and J. Sibert; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+          <t>Recognize the main duo/trio combinations: A. Gakou | J. Sibert and A. Gakou | R. Monteiro.</t>
         </is>
       </c>
     </row>
@@ -1561,6 +1763,18 @@
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>Limited offensive rebounding impact; finishing the first contest usually kills the possession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Do not lose A. Gakou and J. Sibert in help-and-recover situations.</t>
         </is>
@@ -1644,10 +1858,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -1664,69 +1878,69 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.7</v>
+        <v>24.8</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>bench spacer</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26.1</v>
+        <v>24.1</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1736,7 +1950,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1752,13 +1966,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.1</v>
+        <v>23.3</v>
       </c>
       <c r="D5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1779,67 +1993,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_A._SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="D6" t="n">
-        <v>6.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1859,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1967,27 +2181,27 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -2013,23 +2227,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2050,36 +2264,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCB_R._MONTEIRO</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2105,27 +2319,27 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2137,38 +2351,48 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SCB_A._MOREIRA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>42</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>59.5%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>32.8%</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2186,23 +2410,23 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -2222,23 +2446,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
     </row>
@@ -2258,23 +2482,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2294,42 +2518,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SCB_J._SIBERT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>J. Sibert</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -2338,23 +2554,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -2382,23 +2598,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>
@@ -2430,19 +2646,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2670,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2470,23 +2686,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2714,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2518,19 +2734,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2758,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2562,19 +2778,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2802,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2602,23 +2818,111 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SCB_M._KEGLER</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M. Kegler</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="M19" t="n">
         <v>1.8</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>38.5%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_SCB.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,41 +515,41 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -567,26 +567,26 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -619,36 +619,36 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -671,16 +671,16 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -690,17 +690,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -723,21 +723,21 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -775,36 +775,36 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -827,41 +827,41 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -879,39 +879,91 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SCB_M._KEGLER</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Kegler</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
@@ -933,7 +985,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -994,16 +1046,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>53.9</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>98.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="F2" t="n">
-        <v>77.3</v>
+        <v>74.3</v>
       </c>
       <c r="G2" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="3">
@@ -1023,45 +1075,45 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>101.1</v>
+        <v>94.2</v>
       </c>
       <c r="F3" t="n">
-        <v>70.7</v>
+        <v>67.7</v>
       </c>
       <c r="G3" t="n">
-        <v>30.3</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>duo</t>
+          <t>trio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Best net</t>
+          <t>Most used</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Gakou | R. Monteiro</t>
+          <t>A. Gakou | J. Sibert | R. Monteiro</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47.5</v>
+        <v>56.4</v>
       </c>
       <c r="E4" t="n">
-        <v>101.1</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>70.7</v>
+        <v>67.3</v>
       </c>
       <c r="G4" t="n">
-        <v>30.3</v>
+        <v>29.1</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1233,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (14.6 min)</t>
+          <t>A. Gakou | C. Cardoso | J. Sibert | M. Kegler | R. Monteiro (15.3 min)</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1250,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (8.2 net)</t>
+          <t>A. Gakou | C. Cardoso | J. Sibert | M. Kegler | R. Monteiro (26.2 net)</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1284,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -1294,13 +1346,13 @@
         <v>79.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -1310,16 +1362,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>117.1</v>
+        <v>113.5</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="4">
@@ -1329,16 +1381,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.9</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="5">
@@ -1348,16 +1400,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="6">
@@ -1367,16 +1419,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1392,7 +1444,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1411,7 +1463,7 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>-0</v>
@@ -1424,16 +1476,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1449,10 +1501,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1548,7 +1600,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1702,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: A. Gakou, J. Sibert are the first perimeter names you cannot lose in help situations.</t>
+          <t>Closeout discipline matters: M. Correia, A. Gakou are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1756,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with A. Gakou and J. Sibert; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with M. Correia, A. Gakou, and J. Sibert; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1768,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from J. Sibert and M. Kegler; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from C. Cardoso and R. Monteiro; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose A. Gakou and J. Sibert in help-and-recover situations.</t>
+          <t>Do not lose M. Correia and A. Gakou in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1910,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="D2" t="n">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1894,17 +1946,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.8</v>
+        <v>25.3</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1930,17 +1982,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="D4" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1966,17 +2018,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1986,7 +2038,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2002,17 +2054,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="D6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2038,17 +2090,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="D7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E7" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2058,7 +2110,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>primary handler</t>
+          <t>inside scorer</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2172,36 +2224,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SCB_A._GAKOU</t>
+          <t>SCB_M._CORREIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -2218,36 +2270,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -2259,7 +2311,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2273,23 +2325,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2305,41 +2357,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -2356,36 +2408,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_C._CARDOSO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
         <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2397,74 +2449,94 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SCB_R._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>23.3%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>73</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>61.6%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>38.0%</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>45</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>37.8%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>23.4%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SCB_A._MOREIRA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2482,15 +2554,15 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -2498,7 +2570,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
     </row>
@@ -2518,23 +2590,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -2554,42 +2626,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SCB_A._GAKOU</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>A. Gakou</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2598,42 +2662,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SCB_R._MONTEIRO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>R. Monteiro</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2642,23 +2698,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2726,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SCB_J._SIBERT</t>
+          <t>SCB_A._GAKOU</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2686,23 +2742,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>38.8%</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2770,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SCB_V._PANOV</t>
+          <t>SCB_R._MONTEIRO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2734,19 +2790,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -2758,12 +2814,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SCB_A._MOREIRA</t>
+          <t>SCB_J._SIBERT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2774,23 +2830,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -2802,12 +2858,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SCB_C._CARDOSO</t>
+          <t>SCB_V._PANOV</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2818,15 +2874,15 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -2834,7 +2890,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2902,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SCB_M._KEGLER</t>
+          <t>SCB_A._MOREIRA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M. Kegler</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2866,19 +2922,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2946,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SCB_A._SILVA</t>
+          <t>SCB_M._KEGLER</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>M. Kegler</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2906,15 +2962,15 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -2922,7 +2978,95 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SCB_C._CARDOSO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SCB_A._SILVA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
